--- a/import-specification/devices/meter.xlsx
+++ b/import-specification/devices/meter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="137">
   <si>
     <t>Field Type</t>
   </si>
@@ -218,6 +218,12 @@
     <t>Frequency</t>
   </si>
   <si>
+    <t>M_AC_F[1..x]_(MIN|MAX|LATEST)</t>
+  </si>
+  <si>
+    <t>Frequency (min/max/last)</t>
+  </si>
+  <si>
     <t>M_AC_I[1..3]</t>
   </si>
   <si>
@@ -227,6 +233,12 @@
     <t>Current [Phase 1-3]</t>
   </si>
   <si>
+    <t>M_AC_I[1..3]_(MIN|MAX|LATEST)</t>
+  </si>
+  <si>
+    <t>Current (min/max/last)</t>
+  </si>
+  <si>
     <t>M_AC_I_N</t>
   </si>
   <si>
@@ -257,6 +269,12 @@
     <t>Active Power [Phase 1-3]</t>
   </si>
   <si>
+    <t>M_AC_P[1..3]_(MIN|MAX|LATEST)</t>
+  </si>
+  <si>
+    <t>Active power (min/max/last)</t>
+  </si>
+  <si>
     <t>M_AC_PF_COSPHI[1..x]</t>
   </si>
   <si>
@@ -291,6 +309,12 @@
   </si>
   <si>
     <t>Apparent Power [Phase 1-3]</t>
+  </si>
+  <si>
+    <t>M_AC_S[1..3]_(MIN|MAX|LATEST)</t>
+  </si>
+  <si>
+    <t>Apparent power (min/max/last)</t>
   </si>
   <si>
     <t>M_AC_U[1..3]</t>
@@ -753,11 +777,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="35.277" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="70.697" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
@@ -1133,10 +1157,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
         <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1144,10 +1168,10 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
         <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
       </c>
       <c r="D24" t="s">
         <v>71</v>
@@ -1160,6 +1184,9 @@
       <c r="B25" t="s">
         <v>72</v>
       </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
       <c r="D25" t="s">
         <v>73</v>
       </c>
@@ -1172,10 +1199,10 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
         <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1183,13 +1210,10 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1197,13 +1221,13 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
         <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1211,13 +1235,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" t="s">
         <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1225,13 +1249,13 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1239,13 +1263,13 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1253,13 +1277,13 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1267,13 +1291,13 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
         <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1281,13 +1305,13 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
         <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1295,13 +1319,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
         <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1309,10 +1333,10 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
         <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>60</v>
       </c>
       <c r="D36" t="s">
         <v>102</v>
@@ -1326,7 +1350,7 @@
         <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
         <v>104</v>
@@ -1340,7 +1364,7 @@
         <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
         <v>106</v>
@@ -1354,7 +1378,7 @@
         <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -1368,7 +1392,7 @@
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
         <v>110</v>
@@ -1382,7 +1406,7 @@
         <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
         <v>112</v>
@@ -1396,7 +1420,7 @@
         <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
         <v>114</v>
@@ -1410,7 +1434,7 @@
         <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
         <v>116</v>
@@ -1424,7 +1448,7 @@
         <v>117</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
         <v>118</v>
@@ -1438,10 +1462,10 @@
         <v>119</v>
       </c>
       <c r="C45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" t="s">
         <v>120</v>
-      </c>
-      <c r="D45" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1449,6 +1473,12 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1459,6 +1489,9 @@
       <c r="B47" t="s">
         <v>123</v>
       </c>
+      <c r="C47" t="s">
+        <v>40</v>
+      </c>
       <c r="D47" t="s">
         <v>124</v>
       </c>
@@ -1470,6 +1503,9 @@
       <c r="B48" t="s">
         <v>125</v>
       </c>
+      <c r="C48" t="s">
+        <v>40</v>
+      </c>
       <c r="D48" t="s">
         <v>126</v>
       </c>
@@ -1481,8 +1517,52 @@
       <c r="B49" t="s">
         <v>127</v>
       </c>
+      <c r="C49" t="s">
+        <v>128</v>
+      </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
